--- a/experiment2/data_processing/exp_data/06_trimmed.xlsx
+++ b/experiment2/data_processing/exp_data/06_trimmed.xlsx
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>634.3200000000001</v>
+        <v>594.2727272727273</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>558.8461538461538</v>
+        <v>704.5263157894736</v>
       </c>
     </row>
     <row r="22">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>681.8571428571429</v>
+        <v>640.7368421052631</v>
       </c>
     </row>
     <row r="24">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>737.5384615384615</v>
+        <v>719.4</v>
       </c>
     </row>
     <row r="25">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>507.4074074074074</v>
+        <v>513.5384615384615</v>
       </c>
     </row>
     <row r="28">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>676.1538461538462</v>
+        <v>660.36</v>
       </c>
     </row>
     <row r="34">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>682.0769230769231</v>
+        <v>670.28</v>
       </c>
     </row>
     <row r="37">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>452.1</v>
+        <v>441.3157894736842</v>
       </c>
     </row>
     <row r="62">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>714.3333333333334</v>
+        <v>698.4615384615385</v>
       </c>
     </row>
     <row r="63">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>697.5769230769231</v>
+        <v>664.7916666666666</v>
       </c>
     </row>
     <row r="65">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>822.3200000000001</v>
+        <v>838.125</v>
       </c>
     </row>
     <row r="79">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>683.6666666666666</v>
+        <v>670.3448275862069</v>
       </c>
     </row>
     <row r="80">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>644.8076923076923</v>
+        <v>628.84</v>
       </c>
     </row>
     <row r="118">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>637.8148148148148</v>
+        <v>622.3076923076923</v>
       </c>
     </row>
     <row r="119">
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>384.1428571428572</v>
+        <v>380.1481481481482</v>
       </c>
     </row>
     <row r="123">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>597.88</v>
+        <v>581.6666666666666</v>
       </c>
     </row>
     <row r="136">
